--- a/unduhan/latihan-07-penggajian-kunci.xlsx
+++ b/unduhan/latihan-07-penggajian-kunci.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Kunci Jawaban: Penggajian Karyawan Bulanan</t>
   </si>
   <si>
-    <t xml:space="preserve">Latihan 7 dari 24  |  Tingkat: Lanjutan  |  Perkiraan waktu: 60 menit  |  pushexcel.github.io/Pushexcel</t>
+    <t xml:space="preserve">Latihan 7 dari 104  |  Tingkat: Lanjutan  |  Perkiraan waktu: 60 menit  |  pushexcel.github.io/Pushexcel</t>
   </si>
   <si>
     <t xml:space="preserve">Skenario</t>
